--- a/test/data/excel/Products_template.xlsx
+++ b/test/data/excel/Products_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="29">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t xml:space="preserve">SỮA CHUA NẾP CẨM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COCA COLA 500ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sản phẩm không tên</t>
   </si>
 </sst>
 </file>
@@ -307,7 +313,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="35.12"/>
@@ -531,6 +537,40 @@
         <v>23</v>
       </c>
     </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/test/data/excel/Products_template.xlsx
+++ b/test/data/excel/Products_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="30">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sản phẩm không tên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH TRUE MILK</t>
   </si>
 </sst>
 </file>
@@ -562,7 +565,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>14</v>

--- a/test/data/excel/Products_template.xlsx
+++ b/test/data/excel/Products_template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="34">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -43,6 +43,9 @@
     <t xml:space="preserve">Address</t>
   </si>
   <si>
+    <t xml:space="preserve">Unit</t>
+  </si>
+  <si>
     <t xml:space="preserve">PEPSI LON 320 ML</t>
   </si>
   <si>
@@ -52,19 +55,25 @@
     <t xml:space="preserve">PEPSI</t>
   </si>
   <si>
-    <t xml:space="preserve">0987513328</t>
+    <t xml:space="preserve">098-7513328</t>
   </si>
   <si>
     <t xml:space="preserve">202,QUỐC LỘ 13,PHƯỜNG HIỆP BÌNH THÀNH PHỐ HỒ CHÍ MINH VIỆT NAM</t>
   </si>
   <si>
+    <t xml:space="preserve">Thùng</t>
+  </si>
+  <si>
     <t xml:space="preserve">PEPSI 390 ml</t>
   </si>
   <si>
+    <t xml:space="preserve">Lốc</t>
+  </si>
+  <si>
     <t xml:space="preserve">COCACOLA</t>
   </si>
   <si>
-    <t xml:space="preserve">0283896100</t>
+    <t xml:space="preserve">028-3896100</t>
   </si>
   <si>
     <t xml:space="preserve">LÔ C 12,ĐƯỜNG DỌC 2,KHU CÔNG NGHIỆP PHÚ AN,XÃ BẾN LỨC,TỈNH TÂY NINH,VIỆT NAM</t>
@@ -92,6 +101,9 @@
   </si>
   <si>
     <t xml:space="preserve">SỮA THÁI SƠN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chai</t>
   </si>
   <si>
     <t xml:space="preserve">SỮA CHUA PHO MAI HOÀNG</t>
@@ -124,7 +136,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -184,12 +195,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -316,261 +323,304 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="35.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="81.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="81.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6.48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="B2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="0" t="s">
         <v>11</v>
       </c>
+      <c r="G2" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
+      <c r="H3" s="0" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="A4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="G13" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="G14" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="0" t="s">
         <v>15</v>
       </c>
     </row>

--- a/test/data/excel/Products_template.xlsx
+++ b/test/data/excel/Products_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="41">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -100,6 +100,9 @@
     <t xml:space="preserve">SỮA BẮP THÁI SƠN</t>
   </si>
   <si>
+    <t xml:space="preserve">ĂN NHẸ</t>
+  </si>
+  <si>
     <t xml:space="preserve">SỮA THÁI SƠN</t>
   </si>
   <si>
@@ -122,6 +125,24 @@
   </si>
   <si>
     <t xml:space="preserve">TH TRUE MILK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CƠM THỊT KHO TRỨNG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CƠM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NHÀ HÀNG 5 SAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5stars@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, Tân Kỳ Tân Quý, TPHCM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phần</t>
   </si>
 </sst>
 </file>
@@ -323,13 +344,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="35.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="81.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6.48"/>
@@ -524,72 +545,72 @@
         <v>25</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="0" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>9</v>
@@ -606,13 +627,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F14" s="0" t="s">
         <v>17</v>
@@ -622,6 +643,32 @@
       </c>
       <c r="H14" s="0" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="0" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
